--- a/product_upload/packages/43/file.xlsx
+++ b/product_upload/packages/43/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -840,6 +845,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>VULGA 65 mg XR film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-960DC18982C1</t>
         </is>
       </c>
@@ -863,7 +873,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1030,6 +1040,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>UNAIRA 3GM SACHET</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-9BA69FE62BB9</t>
         </is>
       </c>
@@ -1053,7 +1068,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1212,6 +1227,11 @@
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>TOBI PODHALER 28MG</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-A77F069FC39F</t>
         </is>
       </c>
@@ -1235,7 +1255,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1398,6 +1418,11 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>PecFent 100 MCG NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-04F08BEEF976</t>
         </is>
       </c>
@@ -1421,7 +1446,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1590,6 +1615,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>NEXIUM 40MG TAB</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-F4451CED14BB</t>
         </is>
       </c>
@@ -1613,7 +1643,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1776,6 +1806,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>ADANCOR 20 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-37ED8A60C8F8</t>
         </is>
       </c>
@@ -1799,7 +1834,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1966,6 +2001,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>Debilur</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-4629D0207024</t>
         </is>
       </c>
@@ -1989,7 +2029,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2160,6 +2200,11 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>Debilur</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-0B2D7E89616A</t>
         </is>
       </c>
@@ -2183,7 +2228,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2350,6 +2395,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>Debilur</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-B9D139AC5B1C</t>
         </is>
       </c>
@@ -2373,7 +2423,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2540,6 +2590,11 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>CLERON 250MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-11F30EF923D9</t>
         </is>
       </c>
@@ -2563,7 +2618,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2722,6 +2777,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>RESEDRA 1MG/ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-C2C69CFACB7A</t>
         </is>
       </c>
@@ -2745,7 +2805,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2908,6 +2968,11 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>FLOXAG 320MG F.C. TABLET</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-9B4A95B989A4</t>
         </is>
       </c>
@@ -2931,7 +2996,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3094,6 +3159,11 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>FLOXAG 320MG F.C. TABLET</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-9EE2455FCB7F</t>
         </is>
       </c>
@@ -3117,7 +3187,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3280,6 +3350,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>CLERON 500MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-4EEB870C6325</t>
         </is>
       </c>
@@ -3303,7 +3378,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3458,6 +3533,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>PecFent 100 MCG NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-53EEB1BBEEBB</t>
         </is>
       </c>
@@ -3481,7 +3561,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3650,6 +3730,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>NEXIUM 40MG TAB</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-89D2B66D83DE</t>
         </is>
       </c>
@@ -3673,7 +3758,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3832,6 +3917,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>KLENDAM</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-DFBE8882014E</t>
         </is>
       </c>
@@ -3855,7 +3945,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4022,6 +4112,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>Kurenail</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-10772B15E2D3</t>
         </is>
       </c>
@@ -4045,7 +4140,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4204,6 +4299,11 @@
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>DEFRA 120MG DELAYED RELEASE CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-8F21B2CBDAD5</t>
         </is>
       </c>
@@ -4227,7 +4327,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4388,6 +4488,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>FONTAX 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-56C21E5B8246</t>
         </is>
       </c>
@@ -4411,7 +4516,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4574,6 +4679,11 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>DEFRA 240MG DELAYED RELEASE CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-AF8CAD475AB0</t>
         </is>
       </c>
@@ -4597,7 +4707,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4764,6 +4874,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>GARDIA 16MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-19E5E2B5AAA3</t>
         </is>
       </c>
@@ -4787,7 +4902,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4952,6 +5067,11 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>IRIS 0.5 MG/ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-676B7AE2A77E</t>
         </is>
       </c>
@@ -4975,7 +5095,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5146,6 +5266,11 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>GARDIA PLUS 16/12.5MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-05F9B139042A</t>
         </is>
       </c>
@@ -5169,7 +5294,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5344,6 +5469,11 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>MESTINON 60MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-E741BA1AB2FF</t>
         </is>
       </c>
@@ -5367,7 +5497,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5534,6 +5664,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>GARDIA PLUS 8/12.5MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-AC3852971279</t>
         </is>
       </c>
@@ -5557,7 +5692,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5720,6 +5855,11 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>KALMO 8MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-37668B439581</t>
         </is>
       </c>
@@ -5743,7 +5883,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5910,6 +6050,11 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>TRIVACIN 9.5MG/24H TRANSDERMAL PATCHES</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-D0681C5AD134</t>
         </is>
       </c>
@@ -5933,7 +6078,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6104,6 +6249,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>AVOBAN 2% W-W OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-2A6777E9260C</t>
         </is>
       </c>
@@ -6127,7 +6277,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6294,6 +6444,11 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>TRIVACIN 4.6MG/24H TRANSDERMAL PATCHES</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-85FA772B3DEF</t>
         </is>
       </c>
@@ -6317,7 +6472,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6476,6 +6631,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>NEUPRO 4 MG/24 HRS TRANSDERMAL PATCHES</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-D9576873398C</t>
         </is>
       </c>
@@ -6499,7 +6659,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6668,6 +6828,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>DIAOPTIM MR</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-AB8EE43C7836</t>
         </is>
       </c>
@@ -6691,7 +6856,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6862,6 +7027,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>Benlysta</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-C92AC9B33F9A</t>
         </is>
       </c>
@@ -6885,7 +7055,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7056,6 +7226,11 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>Dovato</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-29348960FC77</t>
         </is>
       </c>
@@ -7079,7 +7254,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7242,6 +7417,11 @@
       </c>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>OZERO</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-FC87672F78AC</t>
         </is>
       </c>
@@ -7265,7 +7445,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7428,6 +7608,11 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>OZERO</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-3FBF3B866138</t>
         </is>
       </c>
@@ -7451,7 +7636,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7606,6 +7791,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>OZERO</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-550B9A2C25B7</t>
         </is>
       </c>
@@ -7629,7 +7819,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7796,6 +7986,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>ACRETIN C 1.2% + 0.025 % GEL</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-DBA68CE2B5CE</t>
         </is>
       </c>
@@ -7819,7 +8014,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7974,6 +8169,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>RIBOLISIN EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-709E59FB4D68</t>
         </is>
       </c>
@@ -7997,7 +8197,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8160,6 +8360,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>VIRONTA</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-94D4F027BFF4</t>
         </is>
       </c>
@@ -8183,7 +8388,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8352,6 +8557,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>Pevas</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-870C85AA1867</t>
         </is>
       </c>
@@ -8375,7 +8585,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8544,6 +8754,11 @@
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>Pevas</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-6F09D1184284</t>
         </is>
       </c>
@@ -8567,7 +8782,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8738,6 +8953,11 @@
       </c>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>OLICAN</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-FFCC82A55420</t>
         </is>
       </c>
@@ -8761,7 +8981,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8916,6 +9136,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>D-SEUL 50000 IU SOFT GELATIN CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-9E8025649E45</t>
         </is>
       </c>
@@ -8939,7 +9164,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9102,6 +9327,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>D-SEUL 50000 IU SOFT GELATIN CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-E04602389F39</t>
         </is>
       </c>
@@ -9125,7 +9355,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9288,6 +9518,11 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>BIOCAFFCIT</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-BF374FC595AF</t>
         </is>
       </c>
@@ -9311,7 +9546,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9474,6 +9709,11 @@
       </c>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>AMLOVAN-HCT 10/320/25MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-347CCE9FF90A</t>
         </is>
       </c>
@@ -9497,7 +9737,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9668,6 +9908,11 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>GONISTA 125MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-70E9F8A45B6B</t>
         </is>
       </c>
@@ -9691,7 +9936,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9858,6 +10103,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>GONISTA 62.5MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-7763B32E4E34</t>
         </is>
       </c>
@@ -9881,7 +10131,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10036,6 +10286,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>QATPEN 300MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-37E46C8CEBE9</t>
         </is>
       </c>
@@ -10059,7 +10314,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10222,6 +10477,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>DEVARIN 10MG ORODISPERSIBLE TABLET</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-B0C012847743</t>
         </is>
       </c>
@@ -10245,7 +10505,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10396,6 +10656,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>AUGE CARE EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-5E3A846D0E14</t>
         </is>
       </c>
@@ -10419,7 +10684,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10582,6 +10847,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>BANORIV 2.5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-A4A1F1BCB672</t>
         </is>
       </c>
@@ -10605,7 +10875,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10764,6 +11034,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>HYE MONO EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-AD96906F0947</t>
         </is>
       </c>
@@ -10787,7 +11062,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10946,6 +11221,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>HYE MULTI EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-683CAB620ADC</t>
         </is>
       </c>
@@ -10969,7 +11249,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11128,6 +11408,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>XILOIAL MONO EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-01BB1F41370D</t>
         </is>
       </c>
@@ -11151,7 +11436,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11310,6 +11595,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>XILOIAL EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-F80C4E5B9788</t>
         </is>
       </c>
@@ -11333,7 +11623,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11492,6 +11782,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t xml:space="preserve">DUSPAMEN 200 mg prolonged release capsule </t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-9D39FB62C6D2</t>
         </is>
       </c>
@@ -11515,7 +11810,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11690,6 +11985,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>GLADIO</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-AD9146DA62B4</t>
         </is>
       </c>
@@ -11713,7 +12013,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11880,6 +12180,11 @@
       </c>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>BASALOG ONE</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-41176995FB58</t>
         </is>
       </c>
@@ -11903,7 +12208,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12066,6 +12371,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>BASALOG ONE</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-1B8A74308BEA</t>
         </is>
       </c>
@@ -12089,7 +12399,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12252,6 +12562,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>BASALOG ONE</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-3D3B79C2A036</t>
         </is>
       </c>
@@ -12275,7 +12590,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12434,6 +12749,11 @@
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>ORNIBEL 0.120 mg / 0.015 mg per 24 Hours</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-B164AF753721</t>
         </is>
       </c>
@@ -12457,7 +12777,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12628,6 +12948,11 @@
       </c>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>TRIPLEX B FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-5B66D2FC16E4</t>
         </is>
       </c>
@@ -12651,7 +12976,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12814,6 +13139,11 @@
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>KINZADO</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-9A01A1BEE2E5</t>
         </is>
       </c>
@@ -12837,7 +13167,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13000,6 +13330,11 @@
       </c>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>MIXIF</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-4FDA3018E83A</t>
         </is>
       </c>
@@ -13023,7 +13358,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13186,6 +13521,11 @@
       </c>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>HY-LIGHT</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-2186BD5B84FB</t>
         </is>
       </c>
@@ -13209,7 +13549,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13384,6 +13724,11 @@
       </c>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>COSYREL 5MG/5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-3EAD85393515</t>
         </is>
       </c>
@@ -13407,7 +13752,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13582,6 +13927,11 @@
       </c>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>COSYREL 5MG/10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-ED99B7F5B000</t>
         </is>
       </c>
@@ -13605,7 +13955,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13768,6 +14118,11 @@
       </c>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>ZINOLE 5MG TABLET (30 tablets)</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-C99685869274</t>
         </is>
       </c>
@@ -13791,7 +14146,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13950,6 +14305,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>ZINOLE 10MG TABLET (30 tablets)</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-56CCED102AE3</t>
         </is>
       </c>
@@ -13973,7 +14333,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14132,6 +14492,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>ZINOLE 15MG TABLET (30 tablets)</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-590944A7DC8E</t>
         </is>
       </c>
@@ -14155,7 +14520,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14318,6 +14683,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>APIEXEL</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-17AB35AAEEF2</t>
         </is>
       </c>
@@ -14341,7 +14711,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14500,6 +14870,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>APIEXEL</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-633B36165AA3</t>
         </is>
       </c>
@@ -14523,7 +14898,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14678,6 +15053,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>APIEXEL</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-69CAD1F1C32D</t>
         </is>
       </c>
@@ -14701,7 +15081,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14876,6 +15256,11 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>DYMISTA</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-53B719211A90</t>
         </is>
       </c>
@@ -14899,7 +15284,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15066,6 +15451,11 @@
       </c>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>LISONORM 20 -10</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-3C5091CA5517</t>
         </is>
       </c>
@@ -15089,7 +15479,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15256,6 +15646,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>LISONORM 10 - 5</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-DC0BFC04FF66</t>
         </is>
       </c>
@@ -15279,7 +15674,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15438,6 +15833,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>FANVIL</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-60B51F5ADFBC</t>
         </is>
       </c>
@@ -15461,7 +15861,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15632,6 +16032,11 @@
       </c>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>REOVAIR</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-922DA7E642C8</t>
         </is>
       </c>
@@ -15655,7 +16060,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15826,6 +16231,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>BASAGLAR 100 u/ml Solution For Injection In Pre-Filled Pen</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-AD4BABC30B76</t>
         </is>
       </c>
@@ -15849,7 +16259,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16020,6 +16430,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>TOPFEROL</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-F880AC69EAF7</t>
         </is>
       </c>
@@ -16043,7 +16458,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16202,6 +16617,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>ESPADA 10MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-A54D24942C1D</t>
         </is>
       </c>
@@ -16225,7 +16645,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16388,6 +16808,11 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>ESPADA 20MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-CEA4D3D6A142</t>
         </is>
       </c>
@@ -16411,7 +16836,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16590,6 +17015,11 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>PROLUTEX</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-493F8296919F</t>
         </is>
       </c>
@@ -16613,7 +17043,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16784,6 +17214,11 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>Vislube EYD DROPS</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-EF5E91E450D4</t>
         </is>
       </c>
@@ -16807,7 +17242,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16970,6 +17405,11 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>Olimestra</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-216765974604</t>
         </is>
       </c>
@@ -16993,7 +17433,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17156,6 +17596,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>Olimestra</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-EF3A052D4AF2</t>
         </is>
       </c>
@@ -17179,7 +17624,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17350,6 +17795,11 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>Eralyce</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-4F742E5B3CF6</t>
         </is>
       </c>
@@ -17373,7 +17823,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17544,6 +17994,11 @@
       </c>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>Eralyce</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-5475F38A3985</t>
         </is>
       </c>
@@ -17567,7 +18022,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17734,6 +18189,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>Betavert</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-239B483E0870</t>
         </is>
       </c>
@@ -17757,7 +18217,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17920,6 +18380,11 @@
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>Betavert</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-D946E36E880C</t>
         </is>
       </c>
@@ -17943,7 +18408,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18110,6 +18575,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>Betavert</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-EB04715630A5</t>
         </is>
       </c>
@@ -18133,7 +18603,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18304,6 +18774,11 @@
       </c>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>Dusta</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-4E9182F1735B</t>
         </is>
       </c>
@@ -18327,7 +18802,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18484,6 +18959,11 @@
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>BITENS</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-09FCEB486015</t>
         </is>
       </c>
@@ -18507,7 +18987,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18668,6 +19148,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>BITENS</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-772AE2D9D7F4</t>
         </is>
       </c>
@@ -18691,7 +19176,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18852,6 +19337,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>BITENS</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-86BB8206F28A</t>
         </is>
       </c>
@@ -18875,7 +19365,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19034,6 +19524,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>Etoxib</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-D81645360550</t>
         </is>
       </c>
@@ -19057,7 +19552,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19212,6 +19707,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>Etoxib</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-47225D217FB2</t>
         </is>
       </c>
@@ -19235,7 +19735,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19397,6 +19897,11 @@
         </is>
       </c>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>Etoxib</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-7195787C98F7</t>
         </is>
@@ -19413,7 +19918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19459,100 +19964,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19584,7 +20094,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19599,92 +20109,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-26001</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>483.58</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>397</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19716,7 +20231,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19731,92 +20246,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-48203</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>30.25</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>398</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19848,7 +20368,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19863,92 +20383,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-76848</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>237.79</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>399</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19980,7 +20505,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -19995,92 +20520,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-39601</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>495.99</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>400</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20112,7 +20642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20127,92 +20657,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-34252</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>462.81</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>401</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20244,7 +20779,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20259,92 +20794,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-17483</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>101.75</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>402</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20376,7 +20916,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20391,92 +20931,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-53867</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>135.4</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>403</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20508,7 +21053,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20523,92 +21068,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-23360</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>212.27</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>404</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20640,7 +21190,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20655,92 +21205,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-41275</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>113.88</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>405</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20772,7 +21327,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20787,92 +21342,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-49524</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>231.28</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>406</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20904,7 +21464,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20919,92 +21479,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-92159</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>70.59999999999999</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>407</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21021,7 +21586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21127,6 +21692,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21162,7 +21737,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21227,6 +21802,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-0190D577BA8F</t>
         </is>
@@ -21263,7 +21848,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21328,6 +21913,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-415B40108413</t>
         </is>
@@ -21364,7 +21959,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21429,6 +22024,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-CD004F3D293E</t>
         </is>
@@ -21465,7 +22070,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21530,6 +22135,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-3BF4F80FCB5D</t>
         </is>
@@ -21566,7 +22181,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21631,6 +22246,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-52DA6DD7D0AA</t>
         </is>
@@ -21667,7 +22292,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21732,6 +22357,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-BEAAD7417BD2</t>
         </is>
@@ -21768,7 +22403,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21833,6 +22468,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-F703DDC58D9E</t>
         </is>
@@ -21869,7 +22514,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21934,6 +22579,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-904B55A66844</t>
         </is>
@@ -21970,7 +22625,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22035,6 +22690,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-764DAF84EF1C</t>
         </is>
@@ -22071,7 +22736,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22136,6 +22801,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-4CF0E4AAB177</t>
         </is>
@@ -22172,7 +22847,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22237,6 +22912,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-FC3F60E16728</t>
         </is>
@@ -22273,7 +22958,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22338,6 +23023,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-63FED0B389D1</t>
         </is>
@@ -22374,7 +23069,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22439,6 +23134,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-417B3E81A01D</t>
         </is>
@@ -22475,7 +23180,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22540,6 +23245,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-314AB1B37C46</t>
         </is>
@@ -22576,7 +23291,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22641,6 +23356,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-759B2C9FD658</t>
         </is>
@@ -22677,7 +23402,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22742,6 +23467,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-D7441842A26C</t>
         </is>
@@ -22778,7 +23513,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22843,6 +23578,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-DB01793E8044</t>
         </is>
@@ -22879,7 +23624,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22944,6 +23689,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-01B8A780ED7D</t>
         </is>
@@ -22980,7 +23735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23045,6 +23800,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-A030A595D2A1</t>
         </is>
@@ -23081,7 +23846,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23146,6 +23911,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-71082E8E86FF</t>
         </is>

--- a/product_upload/packages/43/file.xlsx
+++ b/product_upload/packages/43/file.xlsx
@@ -1076,8 +1076,16 @@
           <t>3743516224-418-191375402148</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TOBI PODHALER 28MG</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TOBI PODHALER 28MG detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1263,8 +1271,16 @@
           <t>7306199402-085-373428079440</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PecFent 100 MCG NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>PecFent 100 MCG NASAL SPRAY detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1651,8 +1667,16 @@
           <t>3032752768-864-432145340263</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ADANCOR 20 mg tablet</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ADANCOR 20 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -2431,8 +2455,16 @@
           <t>9640306073-377-056669851854</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLERON 250MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>CLERON 250MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2626,8 +2658,16 @@
           <t>3559997179-028-465964538169</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RESEDRA 1MG/ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>RESEDRA 1MG/ML ORAL SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -2813,8 +2853,16 @@
           <t>0749615996-612-637338777062</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLOXAG 320MG F.C. TABLET</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>FLOXAG 320MG F.C. TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -3004,8 +3052,16 @@
           <t>9799886527-616-936150867991</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLOXAG 320MG F.C. TABLET</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>FLOXAG 320MG F.C. TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3195,8 +3251,16 @@
           <t>3252577685-262-495847989912</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLERON 500MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>CLERON 500MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -3386,8 +3450,16 @@
           <t>5593247465-211-977376626103</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PecFent 100 MCG NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>PecFent 100 MCG NASAL SPRAY detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -3766,8 +3838,16 @@
           <t>6320622875-812-277743429057</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KLENDAM</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>KLENDAM detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -4148,8 +4228,16 @@
           <t>9075538297-770-397254163158</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEFRA 120MG DELAYED RELEASE CAPSULES</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>DEFRA 120MG DELAYED RELEASE CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4335,8 +4423,16 @@
           <t>9039412948-337-117108673416</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FONTAX 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>FONTAX 20 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>AJA PHARMACEUTICAL INDUSTRIES</t>
@@ -4524,8 +4620,16 @@
           <t>7918273785-493-098117944443</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEFRA 240MG DELAYED RELEASE CAPSULES</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>DEFRA 240MG DELAYED RELEASE CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -4910,8 +5014,16 @@
           <t>0435698897-570-526852628058</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ IRIS 0.5 MG/ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>IRIS 0.5 MG/ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -5700,8 +5812,16 @@
           <t>9400021000-327-342383341515</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KALMO 8MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>KALMO 8MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -5891,8 +6011,16 @@
           <t>7790229368-795-946011268292</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TRIVACIN 9.5MG/24H TRANSDERMAL PATCHES</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>TRIVACIN 9.5MG/24H TRANSDERMAL PATCHES detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -6285,8 +6413,16 @@
           <t>1463249183-549-624540558376</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TRIVACIN 4.6MG/24H TRANSDERMAL PATCHES</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>TRIVACIN 4.6MG/24H TRANSDERMAL PATCHES detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -6480,8 +6616,16 @@
           <t>8824785729-108-897861795865</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NEUPRO 4 MG/24 HRS TRANSDERMAL PATCHES</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>NEUPRO 4 MG/24 HRS TRANSDERMAL PATCHES detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -7262,8 +7406,16 @@
           <t>7783896630-647-223370712233</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OZERO</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>OZERO detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7453,8 +7605,16 @@
           <t>8074726282-572-446837707050</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OZERO</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>OZERO detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -7644,8 +7804,16 @@
           <t>1024559866-482-072569576132</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OZERO</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>OZERO detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -8022,8 +8190,16 @@
           <t>6944247886-058-914520715471</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RIBOLISIN EYE DROPS</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>RIBOLISIN EYE DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -8205,8 +8381,16 @@
           <t>2124929934-629-266465329490</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIRONTA</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>VIRONTA detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -8989,8 +9173,16 @@
           <t>5033725064-426-246291108732</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ D-SEUL 50000 IU SOFT GELATIN CAPSULE</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>D-SEUL 50000 IU SOFT GELATIN CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -9363,8 +9555,16 @@
           <t>0903589192-496-221405702975</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BIOCAFFCIT</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>BIOCAFFCIT detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -9554,8 +9754,16 @@
           <t>8932951803-343-639113270713</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AMLOVAN-HCT 10/320/25MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>AMLOVAN-HCT 10/320/25MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
@@ -10139,8 +10347,16 @@
           <t>0371261301-050-079834029799</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QATPEN 300MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>QATPEN 300MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -10513,8 +10729,16 @@
           <t>6435471464-298-954105395045</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AUGE CARE EYE DROPS</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>AUGE CARE EYE DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10692,8 +10916,16 @@
           <t>6129947038-186-345290628353</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BANORIV 2.5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>BANORIV 2.5MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -10883,8 +11115,16 @@
           <t>6776750295-979-766160984827</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HYE MONO EYE DROPS</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>HYE MONO EYE DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -11070,8 +11310,16 @@
           <t>4361221864-533-189409088816</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HYE MULTI EYE DROPS</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>HYE MULTI EYE DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -11257,8 +11505,16 @@
           <t>4925373840-312-009551158082</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ XILOIAL MONO EYE DROPS</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>XILOIAL MONO EYE DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11444,8 +11700,16 @@
           <t>2009278579-621-778544645740</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ XILOIAL EYE DROPS</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>XILOIAL EYE DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11631,8 +11895,16 @@
           <t>7718404174-146-029615887141</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DUSPAMEN 200 mg prolonged release capsule</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>DUSPAMEN 200 mg prolonged release capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -12021,8 +12293,16 @@
           <t>6097643663-207-911624454205</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BASALOG ONE</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>BASALOG ONE detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -12216,8 +12496,16 @@
           <t>3109632686-768-613466955197</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BASALOG ONE</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>BASALOG ONE detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -12407,8 +12695,16 @@
           <t>9368342605-476-285386935172</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BASALOG ONE</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>BASALOG ONE detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12598,8 +12894,16 @@
           <t>4961456894-829-185008195565</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ORNIBEL 0.120 mg / 0.015 mg per 24 Hours</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>ORNIBEL 0.120 mg / 0.015 mg per 24 Hours detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -12984,8 +13288,16 @@
           <t>3258770923-830-018729633214</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KINZADO</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>KINZADO detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -13175,8 +13487,16 @@
           <t>9099296433-523-962086447143</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MIXIF</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>MIXIF detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13366,8 +13686,16 @@
           <t>1315660037-010-265005567644</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HY-LIGHT</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>HY-LIGHT detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13557,8 +13885,16 @@
           <t>1144509807-370-885453387503</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ COSYREL 5MG/5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>COSYREL 5MG/5MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -13760,8 +14096,16 @@
           <t>5682048219-443-128570400484</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ COSYREL 5MG/10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>COSYREL 5MG/10MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -13963,8 +14307,16 @@
           <t>7994611706-963-494997233247</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZINOLE 5MG TABLET (30 tablets)</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>ZINOLE 5MG TABLET (30 tablets) detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -14154,8 +14506,16 @@
           <t>3719514526-319-970512735352</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZINOLE 10MG TABLET (30 tablets)</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>ZINOLE 10MG TABLET (30 tablets) detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -14341,8 +14701,16 @@
           <t>8584635500-587-595467972234</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZINOLE 15MG TABLET (30 tablets)</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>ZINOLE 15MG TABLET (30 tablets) detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -14719,8 +15087,16 @@
           <t>3113563030-498-234431426448</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ APIEXEL</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>APIEXEL detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -14906,8 +15282,16 @@
           <t>8201067696-003-684061615883</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ APIEXEL</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>APIEXEL detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -15292,8 +15676,16 @@
           <t>4182026024-401-924299716362</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LISONORM 20 -10</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>LISONORM 20 -10 detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -15487,8 +15879,16 @@
           <t>0223769907-268-097678247368</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LISONORM 10 - 5</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>LISONORM 10 - 5 detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
@@ -15682,8 +16082,16 @@
           <t>0818688097-975-700221116904</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FANVIL</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>FANVIL detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -16068,8 +16476,16 @@
           <t>8010590643-557-068474366062</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BASAGLAR 100 u/ml Solution For Injection In Pre-Filled Pen</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>BASAGLAR 100 u/ml Solution For Injection In Pre-Filled Pen detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -16466,8 +16882,16 @@
           <t>2787802210-055-640073072503</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ESPADA 10MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>ESPADA 10MG F.C TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16653,8 +17077,16 @@
           <t>1210679446-451-297260156439</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ESPADA 20MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>ESPADA 20MG F.C TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -17250,8 +17682,16 @@
           <t>8105205013-979-996290228605</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Olimestra</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Olimestra detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17441,8 +17881,16 @@
           <t>0144473191-556-499852983040</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Olimestra</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Olimestra detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -18810,8 +19258,16 @@
           <t>3745922688-479-711711709101</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BITENS</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>BITENS detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
           <t>AJA PHARMACEUTICAL INDUSTRIES</t>
@@ -18995,8 +19451,16 @@
           <t>9038614548-277-432921386554</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BITENS</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>BITENS detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
           <t>AJA PHARMACEUTICAL INDUSTRIES</t>
@@ -19184,8 +19648,16 @@
           <t>9363527797-876-597753754542</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BITENS</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>BITENS detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
           <t>AJA PHARMACEUTICAL INDUSTRIES</t>
@@ -19373,8 +19845,16 @@
           <t>3714707058-350-738219809540</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Etoxib</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Etoxib detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
@@ -19560,8 +20040,16 @@
           <t>4357137643-567-703869568851</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Etoxib</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Etoxib detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
@@ -19743,8 +20231,16 @@
           <t>1726784025-527-022371959674</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Etoxib</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Etoxib detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/43/file.xlsx
+++ b/product_upload/packages/43/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20460,7 +20460,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22082,7 +22082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22163,40 +22163,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22276,38 +22281,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>44.17</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-0190D577BA8F</t>
         </is>
@@ -22387,38 +22397,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>449.31</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-415B40108413</t>
         </is>
@@ -22498,38 +22513,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>491.22</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-CD004F3D293E</t>
         </is>
@@ -22609,38 +22629,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>70.3</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-3BF4F80FCB5D</t>
         </is>
@@ -22720,38 +22745,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>465.01</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-52DA6DD7D0AA</t>
         </is>
@@ -22831,38 +22861,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>172.85</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-BEAAD7417BD2</t>
         </is>
@@ -22942,38 +22977,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>131.61</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-F703DDC58D9E</t>
         </is>
@@ -23053,38 +23093,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>485.5</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-904B55A66844</t>
         </is>
@@ -23164,38 +23209,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>68.45999999999999</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-764DAF84EF1C</t>
         </is>
@@ -23275,38 +23325,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>350.27</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-4CF0E4AAB177</t>
         </is>
@@ -23386,38 +23441,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>165.61</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-FC3F60E16728</t>
         </is>
@@ -23497,38 +23557,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>340.53</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-63FED0B389D1</t>
         </is>
@@ -23608,38 +23673,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>212.86</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-417B3E81A01D</t>
         </is>
@@ -23719,38 +23789,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>41.45</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-314AB1B37C46</t>
         </is>
@@ -23830,38 +23905,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>369.08</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-759B2C9FD658</t>
         </is>
@@ -23941,38 +24021,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>178.05</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-D7441842A26C</t>
         </is>
@@ -24052,38 +24137,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>62.88</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-DB01793E8044</t>
         </is>
@@ -24163,38 +24253,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>245.04</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-01B8A780ED7D</t>
         </is>
@@ -24274,38 +24369,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>342.92</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-A030A595D2A1</t>
         </is>
@@ -24385,38 +24485,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>259.95</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-71082E8E86FF</t>
         </is>
